--- a/data/scenarios/food_as_industry.xlsx
+++ b/data/scenarios/food_as_industry.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="98">
   <si>
     <t>f_food</t>
   </si>
@@ -709,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J156"/>
+  <dimension ref="A1:J159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
@@ -1519,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="3">
-        <f t="shared" ref="J47:J58" si="0">2/3</f>
+        <f t="shared" ref="J47:J60" si="0">2/3</f>
         <v>0.66666666666666663</v>
       </c>
     </row>
@@ -1732,22 +1732,26 @@
       <c r="J59" s="6"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
+      <c r="A60" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="J60" s="3">
+        <f>25/29.3</f>
+        <v>0.85324232081911255</v>
+      </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -1760,25 +1764,22 @@
       <c r="J61" s="6"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>69</v>
-      </c>
-      <c r="B62" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" t="s">
-        <v>11</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="J62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
-        <v>70</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
@@ -1795,7 +1796,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
@@ -1812,7 +1813,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
@@ -1829,7 +1830,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
@@ -1845,22 +1846,25 @@
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
+      <c r="A67" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>2</v>
+      </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -1873,25 +1877,22 @@
       <c r="J68" s="6"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>76</v>
-      </c>
-      <c r="B69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" t="s">
-        <v>11</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="J69">
-        <v>2</v>
-      </c>
+      <c r="A69" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
@@ -1903,129 +1904,128 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>78</v>
       </c>
-      <c r="B71" t="s">
-        <v>12</v>
-      </c>
-      <c r="C71" t="s">
-        <v>11</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="J71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
+      <c r="B72" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>80</v>
       </c>
-      <c r="B73" t="s">
-        <v>12</v>
-      </c>
-      <c r="C73" t="s">
-        <v>11</v>
-      </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="J73" s="3">
+      <c r="B74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="J74" s="3">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" t="s">
-        <v>12</v>
-      </c>
-      <c r="C74" t="s">
-        <v>11</v>
-      </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="J74" s="3">
-        <f t="shared" ref="J74:J75" si="1">1/3</f>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="J75" s="3">
+        <f t="shared" ref="J75:J76" si="1">1/3</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>82</v>
       </c>
-      <c r="B75" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" t="s">
-        <v>11</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="J75" s="3">
+      <c r="B76" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="J76" s="3">
         <f t="shared" si="1"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>84</v>
-      </c>
-      <c r="B77" t="s">
-        <v>12</v>
-      </c>
-      <c r="C77" t="s">
-        <v>11</v>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="J77" s="3">
-        <f>2/3</f>
-        <v>0.66666666666666663</v>
-      </c>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
@@ -2078,22 +2078,26 @@
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
+      <c r="A81" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="J81" s="3">
+        <f>2/3</f>
+        <v>0.66666666666666663</v>
+      </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -2107,7 +2111,7 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -2121,7 +2125,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -2133,66 +2137,62 @@
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-      <c r="G86" s="5"/>
-      <c r="H86" s="5"/>
-      <c r="I86" s="5"/>
-      <c r="J86" s="5"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B87" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D87" s="9">
-        <v>1</v>
-      </c>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
+      <c r="B88" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="10"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>16</v>
-      </c>
-      <c r="B89" t="s">
-        <v>96</v>
-      </c>
-      <c r="C89" t="s">
-        <v>97</v>
-      </c>
-      <c r="D89">
-        <v>22</v>
-      </c>
-      <c r="J89">
-        <f>D89-10</f>
-        <v>12</v>
-      </c>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="6"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B90" t="s">
         <v>96</v>
@@ -2200,8 +2200,7 @@
       <c r="C90" t="s">
         <v>97</v>
       </c>
-      <c r="D90" s="11">
-        <f>D89</f>
+      <c r="D90">
         <v>22</v>
       </c>
       <c r="J90">
@@ -2211,7 +2210,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B91" t="s">
         <v>96</v>
@@ -2219,16 +2218,18 @@
       <c r="C91" t="s">
         <v>97</v>
       </c>
-      <c r="D91">
-        <v>100</v>
+      <c r="D91" s="11">
+        <f>D90</f>
+        <v>22</v>
       </c>
       <c r="J91">
-        <v>100</v>
+        <f>D91-10</f>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B92" t="s">
         <v>96</v>
@@ -2237,15 +2238,15 @@
         <v>97</v>
       </c>
       <c r="D92">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B93" t="s">
         <v>96</v>
@@ -2253,8 +2254,7 @@
       <c r="C93" t="s">
         <v>97</v>
       </c>
-      <c r="D93" s="11">
-        <f>D92</f>
+      <c r="D93">
         <v>4</v>
       </c>
       <c r="J93">
@@ -2263,7 +2263,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B94" t="s">
         <v>96</v>
@@ -2271,17 +2271,17 @@
       <c r="C94" t="s">
         <v>97</v>
       </c>
-      <c r="D94">
-        <v>100</v>
+      <c r="D94" s="11">
+        <f>D93</f>
+        <v>4</v>
       </c>
       <c r="J94">
-        <f>D94-10</f>
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B95" t="s">
         <v>96</v>
@@ -2290,15 +2290,16 @@
         <v>97</v>
       </c>
       <c r="D95">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="J95">
-        <v>0</v>
+        <f>D95-10</f>
+        <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B96" t="s">
         <v>96</v>
@@ -2306,8 +2307,7 @@
       <c r="C96" t="s">
         <v>97</v>
       </c>
-      <c r="D96" s="11">
-        <f>D95</f>
+      <c r="D96">
         <v>8</v>
       </c>
       <c r="J96">
@@ -2316,7 +2316,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B97" t="s">
         <v>96</v>
@@ -2324,8 +2324,9 @@
       <c r="C97" t="s">
         <v>97</v>
       </c>
-      <c r="D97">
-        <v>1</v>
+      <c r="D97" s="11">
+        <f>D96</f>
+        <v>8</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -2333,7 +2334,7 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B98" t="s">
         <v>96</v>
@@ -2341,8 +2342,7 @@
       <c r="C98" t="s">
         <v>97</v>
       </c>
-      <c r="D98" s="11">
-        <f>D97</f>
+      <c r="D98">
         <v>1</v>
       </c>
       <c r="J98">
@@ -2351,7 +2351,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B99" t="s">
         <v>96</v>
@@ -2359,17 +2359,17 @@
       <c r="C99" t="s">
         <v>97</v>
       </c>
-      <c r="D99" s="4">
-        <v>22</v>
+      <c r="D99" s="11">
+        <f>D98</f>
+        <v>1</v>
       </c>
       <c r="J99">
-        <f>D99-10</f>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B100" t="s">
         <v>96</v>
@@ -2377,8 +2377,7 @@
       <c r="C100" t="s">
         <v>97</v>
       </c>
-      <c r="D100" s="11">
-        <f>D99</f>
+      <c r="D100" s="4">
         <v>22</v>
       </c>
       <c r="J100">
@@ -2387,45 +2386,41 @@
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" s="6" t="s">
+      <c r="A101" t="s">
+        <v>27</v>
+      </c>
+      <c r="B101" t="s">
+        <v>96</v>
+      </c>
+      <c r="C101" t="s">
+        <v>97</v>
+      </c>
+      <c r="D101" s="11">
+        <f>D100</f>
+        <v>22</v>
+      </c>
+      <c r="J101">
+        <f>D101-10</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="10"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B102" t="s">
-        <v>96</v>
-      </c>
-      <c r="C102" t="s">
-        <v>97</v>
-      </c>
-      <c r="D102" s="7">
-        <v>16</v>
-      </c>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="7"/>
-      <c r="H102" s="7"/>
-      <c r="I102" s="7"/>
-      <c r="J102">
-        <f>D102-10</f>
-        <v>6</v>
-      </c>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="10"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="6"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B103" t="s">
         <v>96</v>
@@ -2448,7 +2443,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B104" t="s">
         <v>96</v>
@@ -2471,7 +2466,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B105" t="s">
         <v>96</v>
@@ -2493,45 +2488,45 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="6" t="s">
+      <c r="A106" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B106" t="s">
+        <v>96</v>
+      </c>
+      <c r="C106" t="s">
+        <v>97</v>
+      </c>
+      <c r="D106" s="7">
+        <v>16</v>
+      </c>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="7"/>
+      <c r="J106">
+        <f>D106-10</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="10"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="6"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B107" t="s">
-        <v>96</v>
-      </c>
-      <c r="C107" t="s">
-        <v>97</v>
-      </c>
-      <c r="D107" s="7">
-        <v>85</v>
-      </c>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
-      <c r="I107" s="7"/>
-      <c r="J107">
-        <f>D107-10</f>
-        <v>75</v>
-      </c>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="10"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6"/>
+      <c r="J107" s="6"/>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B108" t="s">
         <v>96</v>
@@ -2548,13 +2543,13 @@
       <c r="H108" s="7"/>
       <c r="I108" s="7"/>
       <c r="J108">
-        <f>D108-10</f>
+        <f t="shared" ref="J108:J115" si="2">D108-10</f>
         <v>75</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B109" t="s">
         <v>96</v>
@@ -2571,13 +2566,13 @@
       <c r="H109" s="7"/>
       <c r="I109" s="7"/>
       <c r="J109">
-        <f>D109-10</f>
+        <f t="shared" si="2"/>
         <v>75</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B110" t="s">
         <v>96</v>
@@ -2586,7 +2581,7 @@
         <v>97</v>
       </c>
       <c r="D110" s="7">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E110" s="7"/>
       <c r="F110" s="7"/>
@@ -2594,13 +2589,13 @@
       <c r="H110" s="7"/>
       <c r="I110" s="7"/>
       <c r="J110">
-        <f>D110-10</f>
-        <v>85</v>
+        <f t="shared" si="2"/>
+        <v>75</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B111" t="s">
         <v>96</v>
@@ -2608,8 +2603,8 @@
       <c r="C111" t="s">
         <v>97</v>
       </c>
-      <c r="D111" s="4">
-        <v>97</v>
+      <c r="D111" s="7">
+        <v>95</v>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="7"/>
@@ -2617,13 +2612,13 @@
       <c r="H111" s="7"/>
       <c r="I111" s="7"/>
       <c r="J111">
-        <f>D111-10</f>
-        <v>87</v>
+        <f t="shared" si="2"/>
+        <v>85</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B112" t="s">
         <v>96</v>
@@ -2631,8 +2626,8 @@
       <c r="C112" t="s">
         <v>97</v>
       </c>
-      <c r="D112" s="7">
-        <v>29</v>
+      <c r="D112" s="4">
+        <v>97</v>
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="7"/>
@@ -2640,13 +2635,13 @@
       <c r="H112" s="7"/>
       <c r="I112" s="7"/>
       <c r="J112">
-        <f>D112-10</f>
-        <v>19</v>
+        <f t="shared" si="2"/>
+        <v>87</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B113" t="s">
         <v>96</v>
@@ -2654,8 +2649,8 @@
       <c r="C113" t="s">
         <v>97</v>
       </c>
-      <c r="D113" s="4">
-        <v>50</v>
+      <c r="D113" s="7">
+        <v>29</v>
       </c>
       <c r="E113" s="7"/>
       <c r="F113" s="7"/>
@@ -2663,13 +2658,13 @@
       <c r="H113" s="7"/>
       <c r="I113" s="7"/>
       <c r="J113">
-        <f>D113-10</f>
-        <v>40</v>
+        <f t="shared" si="2"/>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B114" t="s">
         <v>96</v>
@@ -2678,7 +2673,7 @@
         <v>97</v>
       </c>
       <c r="D114" s="4">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="E114" s="7"/>
       <c r="F114" s="7"/>
@@ -2686,49 +2681,50 @@
       <c r="H114" s="7"/>
       <c r="I114" s="7"/>
       <c r="J114">
-        <f>D114-10</f>
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B115" t="s">
+        <v>96</v>
+      </c>
+      <c r="C115" t="s">
+        <v>97</v>
+      </c>
+      <c r="D115" s="4">
+        <v>90</v>
+      </c>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
+      <c r="I115" s="7"/>
+      <c r="J115">
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115" s="6" t="s">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="10"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="6"/>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B116" t="s">
-        <v>96</v>
-      </c>
-      <c r="C116" t="s">
-        <v>97</v>
-      </c>
-      <c r="D116">
-        <v>7</v>
-      </c>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
-      <c r="I116" s="7"/>
-      <c r="J116">
-        <v>0</v>
-      </c>
+      <c r="B116" s="6"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="10"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="6"/>
+      <c r="H116" s="6"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B117" t="s">
         <v>96</v>
@@ -2736,8 +2732,8 @@
       <c r="C117" t="s">
         <v>97</v>
       </c>
-      <c r="D117" s="7">
-        <v>35</v>
+      <c r="D117">
+        <v>7</v>
       </c>
       <c r="E117" s="7"/>
       <c r="F117" s="7"/>
@@ -2745,13 +2741,12 @@
       <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117">
-        <f>D117-10</f>
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B118" t="s">
         <v>96</v>
@@ -2760,7 +2755,7 @@
         <v>97</v>
       </c>
       <c r="D118" s="7">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="7"/>
@@ -2768,13 +2763,13 @@
       <c r="H118" s="7"/>
       <c r="I118" s="7"/>
       <c r="J118">
-        <f>D118-10</f>
-        <v>53</v>
+        <f t="shared" ref="J118:J126" si="3">D118-10</f>
+        <v>25</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B119" t="s">
         <v>96</v>
@@ -2783,7 +2778,7 @@
         <v>97</v>
       </c>
       <c r="D119" s="7">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E119" s="7"/>
       <c r="F119" s="7"/>
@@ -2791,13 +2786,13 @@
       <c r="H119" s="7"/>
       <c r="I119" s="7"/>
       <c r="J119">
-        <f>D119-10</f>
-        <v>44</v>
+        <f t="shared" si="3"/>
+        <v>53</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B120" t="s">
         <v>96</v>
@@ -2805,8 +2800,8 @@
       <c r="C120" t="s">
         <v>97</v>
       </c>
-      <c r="D120" s="4">
-        <v>75</v>
+      <c r="D120" s="7">
+        <v>54</v>
       </c>
       <c r="E120" s="7"/>
       <c r="F120" s="7"/>
@@ -2814,13 +2809,13 @@
       <c r="H120" s="7"/>
       <c r="I120" s="7"/>
       <c r="J120">
-        <f>D120-10</f>
-        <v>65</v>
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B121" t="s">
         <v>96</v>
@@ -2828,8 +2823,8 @@
       <c r="C121" t="s">
         <v>97</v>
       </c>
-      <c r="D121" s="7">
-        <v>10</v>
+      <c r="D121" s="4">
+        <v>75</v>
       </c>
       <c r="E121" s="7"/>
       <c r="F121" s="7"/>
@@ -2837,13 +2832,13 @@
       <c r="H121" s="7"/>
       <c r="I121" s="7"/>
       <c r="J121">
-        <f>D121-10</f>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>65</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B122" t="s">
         <v>96</v>
@@ -2852,7 +2847,7 @@
         <v>97</v>
       </c>
       <c r="D122" s="7">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="E122" s="7"/>
       <c r="F122" s="7"/>
@@ -2860,13 +2855,13 @@
       <c r="H122" s="7"/>
       <c r="I122" s="7"/>
       <c r="J122">
-        <f>D122-10</f>
-        <v>80</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B123" t="s">
         <v>96</v>
@@ -2875,7 +2870,7 @@
         <v>97</v>
       </c>
       <c r="D123" s="7">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="E123" s="7"/>
       <c r="F123" s="7"/>
@@ -2883,13 +2878,13 @@
       <c r="H123" s="7"/>
       <c r="I123" s="7"/>
       <c r="J123">
-        <f>D123-10</f>
-        <v>36</v>
+        <f t="shared" si="3"/>
+        <v>80</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B124" t="s">
         <v>96</v>
@@ -2898,7 +2893,7 @@
         <v>97</v>
       </c>
       <c r="D124" s="7">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="E124" s="7"/>
       <c r="F124" s="7"/>
@@ -2906,13 +2901,13 @@
       <c r="H124" s="7"/>
       <c r="I124" s="7"/>
       <c r="J124">
-        <f>D124-10</f>
-        <v>90</v>
+        <f t="shared" si="3"/>
+        <v>36</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B125" t="s">
         <v>96</v>
@@ -2920,8 +2915,8 @@
       <c r="C125" t="s">
         <v>97</v>
       </c>
-      <c r="D125" s="4">
-        <v>90</v>
+      <c r="D125" s="7">
+        <v>100</v>
       </c>
       <c r="E125" s="7"/>
       <c r="F125" s="7"/>
@@ -2929,60 +2924,60 @@
       <c r="H125" s="7"/>
       <c r="I125" s="7"/>
       <c r="J125">
-        <f>D125-10</f>
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B126" t="s">
+        <v>96</v>
+      </c>
+      <c r="C126" t="s">
+        <v>97</v>
+      </c>
+      <c r="D126" s="4">
+        <v>90</v>
+      </c>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7"/>
+      <c r="G126" s="7"/>
+      <c r="H126" s="7"/>
+      <c r="I126" s="7"/>
+      <c r="J126">
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" s="6" t="s">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="10"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="s">
+      <c r="B127" s="6"/>
+      <c r="C127" s="6"/>
+      <c r="D127" s="10"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="6"/>
+      <c r="I127" s="6"/>
+      <c r="J127" s="6"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B127" t="s">
-        <v>96</v>
-      </c>
-      <c r="C127" t="s">
-        <v>97</v>
-      </c>
-      <c r="D127" s="12">
+      <c r="B128" t="s">
+        <v>96</v>
+      </c>
+      <c r="C128" t="s">
+        <v>97</v>
+      </c>
+      <c r="D128" s="12">
         <f>8.5*20/(29.5+8.5)</f>
         <v>4.4736842105263159</v>
-      </c>
-      <c r="E127" s="4"/>
-      <c r="F127" s="4"/>
-      <c r="G127" s="4"/>
-      <c r="H127" s="4"/>
-      <c r="I127" s="4"/>
-      <c r="J127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B128" t="s">
-        <v>96</v>
-      </c>
-      <c r="C128" t="s">
-        <v>97</v>
-      </c>
-      <c r="D128" s="12">
-        <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)</f>
-        <v>2.981366459627329</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
@@ -2995,7 +2990,7 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B129" t="s">
         <v>96</v>
@@ -3004,8 +2999,8 @@
         <v>97</v>
       </c>
       <c r="D129" s="12">
-        <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)</f>
-        <v>7.723292469352014</v>
+        <f>(80.7*0+14.4*20+0.3*5*0)/(80.7+14.4+0.3*5)</f>
+        <v>2.981366459627329</v>
       </c>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
@@ -3018,7 +3013,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B130" t="s">
         <v>96</v>
@@ -3026,9 +3021,9 @@
       <c r="C130" t="s">
         <v>97</v>
       </c>
-      <c r="D130">
-        <f>60</f>
-        <v>60</v>
+      <c r="D130" s="12">
+        <f>(45.6*0+44.1*20+1.3*5*0+1.8*10*0)/(45.6+44.1+1.3*5+1.8*10)</f>
+        <v>7.723292469352014</v>
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
@@ -3036,13 +3031,12 @@
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
       <c r="J130">
-        <f>D130-10</f>
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B131" t="s">
         <v>96</v>
@@ -3051,7 +3045,8 @@
         <v>97</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <f>60</f>
+        <v>60</v>
       </c>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
@@ -3059,12 +3054,13 @@
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
       <c r="J131">
-        <v>0</v>
+        <f>D131-10</f>
+        <v>50</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B132" t="s">
         <v>96</v>
@@ -3073,7 +3069,7 @@
         <v>97</v>
       </c>
       <c r="D132">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
@@ -3081,13 +3077,12 @@
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
       <c r="J132">
-        <f>D132-10</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B133" t="s">
         <v>96</v>
@@ -3110,7 +3105,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B134" t="s">
         <v>96</v>
@@ -3133,7 +3128,7 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B135" t="s">
         <v>96</v>
@@ -3142,8 +3137,7 @@
         <v>97</v>
       </c>
       <c r="D135">
-        <f>43</f>
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
@@ -3152,43 +3146,50 @@
       <c r="I135" s="4"/>
       <c r="J135">
         <f>D135-10</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B136" t="s">
+        <v>96</v>
+      </c>
+      <c r="C136" t="s">
+        <v>97</v>
+      </c>
+      <c r="D136">
+        <f>43</f>
+        <v>43</v>
+      </c>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4"/>
+      <c r="G136" s="4"/>
+      <c r="H136" s="4"/>
+      <c r="I136" s="4"/>
+      <c r="J136">
+        <f>D136-10</f>
         <v>33</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" s="6" t="s">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="10"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="6"/>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>13</v>
-      </c>
-      <c r="B137" t="s">
-        <v>96</v>
-      </c>
-      <c r="C137" t="s">
-        <v>97</v>
-      </c>
-      <c r="D137">
-        <v>37</v>
-      </c>
-      <c r="J137">
-        <v>5</v>
-      </c>
+      <c r="B137" s="6"/>
+      <c r="C137" s="6"/>
+      <c r="D137" s="10"/>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="6"/>
+      <c r="H137" s="6"/>
+      <c r="I137" s="6"/>
+      <c r="J137" s="6"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="B138" t="s">
         <v>96</v>
@@ -3196,8 +3197,8 @@
       <c r="C138" t="s">
         <v>97</v>
       </c>
-      <c r="D138" s="7">
-        <v>43</v>
+      <c r="D138">
+        <v>37</v>
       </c>
       <c r="J138">
         <v>5</v>
@@ -3205,7 +3206,7 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B139" t="s">
         <v>96</v>
@@ -3214,114 +3215,94 @@
         <v>97</v>
       </c>
       <c r="D139" s="7">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J139">
         <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" s="6" t="s">
+      <c r="A140" t="s">
+        <v>65</v>
+      </c>
+      <c r="B140" t="s">
+        <v>96</v>
+      </c>
+      <c r="C140" t="s">
+        <v>97</v>
+      </c>
+      <c r="D140" s="7">
+        <v>36</v>
+      </c>
+      <c r="J140">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B141" s="6"/>
+      <c r="C141" s="6"/>
+      <c r="D141" s="10"/>
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
+      <c r="G141" s="6"/>
+      <c r="H141" s="6"/>
+      <c r="I141" s="6"/>
+      <c r="J141" s="6"/>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>66</v>
+      </c>
+      <c r="B142" t="s">
+        <v>96</v>
+      </c>
+      <c r="C142" t="s">
+        <v>97</v>
+      </c>
+      <c r="D142" s="7">
+        <v>12</v>
+      </c>
+      <c r="J142">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B140" s="6"/>
-      <c r="C140" s="6"/>
-      <c r="D140" s="10"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="B143" s="6"/>
+      <c r="C143" s="6"/>
+      <c r="D143" s="10"/>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
+      <c r="G143" s="6"/>
+      <c r="H143" s="6"/>
+      <c r="I143" s="6"/>
+      <c r="J143" s="6"/>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>69</v>
       </c>
-      <c r="B141" t="s">
-        <v>96</v>
-      </c>
-      <c r="C141" t="s">
-        <v>97</v>
-      </c>
-      <c r="D141">
+      <c r="B144" t="s">
+        <v>96</v>
+      </c>
+      <c r="C144" t="s">
+        <v>97</v>
+      </c>
+      <c r="D144">
         <v>5</v>
       </c>
-      <c r="J141">
+      <c r="J144">
         <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A142" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B142" t="s">
-        <v>96</v>
-      </c>
-      <c r="C142" t="s">
-        <v>97</v>
-      </c>
-      <c r="D142">
-        <v>0.4</v>
-      </c>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
-      <c r="G142" s="8"/>
-      <c r="H142" s="8"/>
-      <c r="I142" s="8"/>
-      <c r="J142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A143" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B143" t="s">
-        <v>96</v>
-      </c>
-      <c r="C143" t="s">
-        <v>97</v>
-      </c>
-      <c r="D143" s="4">
-        <v>95</v>
-      </c>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
-      <c r="G143" s="8"/>
-      <c r="H143" s="8"/>
-      <c r="I143" s="8"/>
-      <c r="J143">
-        <f>D143-10</f>
-        <v>85</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A144" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B144" t="s">
-        <v>96</v>
-      </c>
-      <c r="C144" t="s">
-        <v>97</v>
-      </c>
-      <c r="D144">
-        <v>100</v>
-      </c>
-      <c r="E144" s="8"/>
-      <c r="F144" s="8"/>
-      <c r="G144" s="8"/>
-      <c r="H144" s="8"/>
-      <c r="I144" s="8"/>
-      <c r="J144">
-        <f>D144-10</f>
-        <v>90</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B145" t="s">
         <v>96</v>
@@ -3330,7 +3311,7 @@
         <v>97</v>
       </c>
       <c r="D145">
-        <v>100</v>
+        <v>0.4</v>
       </c>
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
@@ -3338,27 +3319,35 @@
       <c r="H145" s="8"/>
       <c r="I145" s="8"/>
       <c r="J145">
-        <f>D145-10</f>
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="10"/>
-      <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
-      <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="6"/>
-      <c r="J146" s="6"/>
+      <c r="A146" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B146" t="s">
+        <v>96</v>
+      </c>
+      <c r="C146" t="s">
+        <v>97</v>
+      </c>
+      <c r="D146" s="4">
+        <v>95</v>
+      </c>
+      <c r="E146" s="8"/>
+      <c r="F146" s="8"/>
+      <c r="G146" s="8"/>
+      <c r="H146" s="8"/>
+      <c r="I146" s="8"/>
+      <c r="J146">
+        <f>D146-10</f>
+        <v>85</v>
+      </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>76</v>
+      <c r="A147" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="B147" t="s">
         <v>96</v>
@@ -3366,49 +3355,59 @@
       <c r="C147" t="s">
         <v>97</v>
       </c>
-      <c r="D147" s="13">
-        <v>52</v>
-      </c>
+      <c r="D147">
+        <v>100</v>
+      </c>
+      <c r="E147" s="8"/>
+      <c r="F147" s="8"/>
+      <c r="G147" s="8"/>
+      <c r="H147" s="8"/>
+      <c r="I147" s="8"/>
       <c r="J147">
         <f>D147-10</f>
-        <v>42</v>
+        <v>90</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B148" s="6"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="10"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="6"/>
-      <c r="J148" s="6"/>
+      <c r="A148" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B148" t="s">
+        <v>96</v>
+      </c>
+      <c r="C148" t="s">
+        <v>97</v>
+      </c>
+      <c r="D148">
+        <v>100</v>
+      </c>
+      <c r="E148" s="8"/>
+      <c r="F148" s="8"/>
+      <c r="G148" s="8"/>
+      <c r="H148" s="8"/>
+      <c r="I148" s="8"/>
+      <c r="J148">
+        <f>D148-10</f>
+        <v>90</v>
+      </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>80</v>
-      </c>
-      <c r="B149" t="s">
-        <v>96</v>
-      </c>
-      <c r="C149" t="s">
-        <v>97</v>
-      </c>
-      <c r="D149" s="4">
-        <v>24</v>
-      </c>
-      <c r="J149">
-        <f>D149-10</f>
-        <v>14</v>
-      </c>
+      <c r="A149" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B149" s="6"/>
+      <c r="C149" s="6"/>
+      <c r="D149" s="10"/>
+      <c r="E149" s="6"/>
+      <c r="F149" s="6"/>
+      <c r="G149" s="6"/>
+      <c r="H149" s="6"/>
+      <c r="I149" s="6"/>
+      <c r="J149" s="6"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B150" t="s">
         <v>96</v>
@@ -3416,50 +3415,49 @@
       <c r="C150" t="s">
         <v>97</v>
       </c>
-      <c r="D150" s="11">
-        <f>D149</f>
-        <v>24</v>
+      <c r="D150" s="13">
+        <v>52</v>
       </c>
       <c r="J150">
         <f>D150-10</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B151" s="6"/>
+      <c r="C151" s="6"/>
+      <c r="D151" s="10"/>
+      <c r="E151" s="6"/>
+      <c r="F151" s="6"/>
+      <c r="G151" s="6"/>
+      <c r="H151" s="6"/>
+      <c r="I151" s="6"/>
+      <c r="J151" s="6"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>80</v>
+      </c>
+      <c r="B152" t="s">
+        <v>96</v>
+      </c>
+      <c r="C152" t="s">
+        <v>97</v>
+      </c>
+      <c r="D152" s="4">
+        <v>24</v>
+      </c>
+      <c r="J152">
+        <f>D152-10</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>82</v>
-      </c>
-      <c r="B151" t="s">
-        <v>96</v>
-      </c>
-      <c r="C151" t="s">
-        <v>97</v>
-      </c>
-      <c r="D151">
-        <v>61</v>
-      </c>
-      <c r="J151">
-        <f>D151-10</f>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A152" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B152" s="6"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="10"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="6"/>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B153" t="s">
         <v>96</v>
@@ -3467,16 +3465,18 @@
       <c r="C153" t="s">
         <v>97</v>
       </c>
-      <c r="D153">
-        <v>100</v>
+      <c r="D153" s="11">
+        <f>D152</f>
+        <v>24</v>
       </c>
       <c r="J153">
-        <v>100</v>
+        <f>D153-10</f>
+        <v>14</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B154" t="s">
         <v>96</v>
@@ -3485,49 +3485,99 @@
         <v>97</v>
       </c>
       <c r="D154">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="J154">
-        <v>0</v>
+        <f>D154-10</f>
+        <v>51</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>86</v>
-      </c>
-      <c r="B155" t="s">
-        <v>96</v>
-      </c>
-      <c r="C155" t="s">
-        <v>97</v>
-      </c>
-      <c r="D155">
-        <v>85</v>
-      </c>
-      <c r="J155">
-        <f>D155-10</f>
-        <v>75</v>
-      </c>
+      <c r="A155" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B155" s="6"/>
+      <c r="C155" s="6"/>
+      <c r="D155" s="10"/>
+      <c r="E155" s="6"/>
+      <c r="F155" s="6"/>
+      <c r="G155" s="6"/>
+      <c r="H155" s="6"/>
+      <c r="I155" s="6"/>
+      <c r="J155" s="6"/>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>84</v>
+      </c>
+      <c r="B156" t="s">
+        <v>96</v>
+      </c>
+      <c r="C156" t="s">
+        <v>97</v>
+      </c>
+      <c r="D156">
+        <v>100</v>
+      </c>
+      <c r="J156">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>85</v>
+      </c>
+      <c r="B157" t="s">
+        <v>96</v>
+      </c>
+      <c r="C157" t="s">
+        <v>97</v>
+      </c>
+      <c r="D157">
+        <v>4</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>86</v>
+      </c>
+      <c r="B158" t="s">
+        <v>96</v>
+      </c>
+      <c r="C158" t="s">
+        <v>97</v>
+      </c>
+      <c r="D158">
+        <v>85</v>
+      </c>
+      <c r="J158">
+        <f>D158-10</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>87</v>
       </c>
-      <c r="B156" t="s">
-        <v>96</v>
-      </c>
-      <c r="C156" t="s">
-        <v>97</v>
-      </c>
-      <c r="D156">
+      <c r="B159" t="s">
+        <v>96</v>
+      </c>
+      <c r="C159" t="s">
+        <v>97</v>
+      </c>
+      <c r="D159">
         <v>22</v>
       </c>
-      <c r="J156">
-        <f>D156-10</f>
+      <c r="J159">
+        <f>D159-10</f>
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/scenarios/food_as_industry.xlsx
+++ b/data/scenarios/food_as_industry.xlsx
@@ -4,10 +4,17 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11550" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="DemandAndConversions" sheetId="2" r:id="rId1"/>
+    <sheet name="Regions" sheetId="7" r:id="rId1"/>
+    <sheet name="DemandAndConversions" sheetId="2" r:id="rId2"/>
+    <sheet name="CropProduction" sheetId="6" r:id="rId3"/>
+    <sheet name="CattleHerd" sheetId="3" r:id="rId4"/>
+    <sheet name="PigHerd" sheetId="4" r:id="rId5"/>
+    <sheet name="FeedMgmt" sheetId="9" r:id="rId6"/>
+    <sheet name="MachineryAndEnergyMgmt" sheetId="8" r:id="rId7"/>
+    <sheet name="motivations" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="137">
   <si>
     <t>f_food</t>
   </si>
@@ -313,6 +320,123 @@
   </si>
   <si>
     <t>abs</t>
+  </si>
+  <si>
+    <t>f_breed</t>
+  </si>
+  <si>
+    <t>dairy</t>
+  </si>
+  <si>
+    <t>milk_prod</t>
+  </si>
+  <si>
+    <t>over 10 years</t>
+  </si>
+  <si>
+    <t>growing pigs</t>
+  </si>
+  <si>
+    <t>feed_energy_per_growth</t>
+  </si>
+  <si>
+    <t>finishing pigs</t>
+  </si>
+  <si>
+    <t>f_animal</t>
+  </si>
+  <si>
+    <t>MJ NE/kg w.g.</t>
+  </si>
+  <si>
+    <t>PIGS</t>
+  </si>
+  <si>
+    <t>Mortality</t>
+  </si>
+  <si>
+    <t>Growing/finishing pigs energy per kg weight gain</t>
+  </si>
+  <si>
+    <t>growing/finishing</t>
+  </si>
+  <si>
+    <t>yield</t>
+  </si>
+  <si>
+    <t>cropland</t>
+  </si>
+  <si>
+    <t>max_land_use_factor</t>
+  </si>
+  <si>
+    <t>f_land_use</t>
+  </si>
+  <si>
+    <t>field machinery</t>
+  </si>
+  <si>
+    <t>diesel</t>
+  </si>
+  <si>
+    <t>energy_source_share</t>
+  </si>
+  <si>
+    <t>biodiesel</t>
+  </si>
+  <si>
+    <t>hydrogen</t>
+  </si>
+  <si>
+    <t>electricity</t>
+  </si>
+  <si>
+    <t>f_activity</t>
+  </si>
+  <si>
+    <t>f_energy_source</t>
+  </si>
+  <si>
+    <t>greenhouse</t>
+  </si>
+  <si>
+    <t>semi-natural grasslands</t>
+  </si>
+  <si>
+    <t>cows</t>
+  </si>
+  <si>
+    <t>enteric_adj</t>
+  </si>
+  <si>
+    <t>f_species</t>
+  </si>
+  <si>
+    <t>cattle</t>
+  </si>
+  <si>
+    <t>bulls</t>
+  </si>
+  <si>
+    <t>beef</t>
+  </si>
+  <si>
+    <t>slaughter_share_male_as_steers</t>
+  </si>
+  <si>
+    <t>f_prod_system</t>
+  </si>
+  <si>
+    <t>slaughter_weight</t>
+  </si>
+  <si>
+    <t>f_crop</t>
+  </si>
+  <si>
+    <t>Semi-natural pastures</t>
+  </si>
+  <si>
+    <t>Semi-natural meadows</t>
   </si>
 </sst>
 </file>
@@ -322,7 +446,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,8 +505,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -401,8 +541,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -410,11 +556,92 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -429,9 +656,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -444,6 +689,1837 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.27866797900262469"/>
+                  <c:y val="-0.48056333119807854"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>motivations!$B$7:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2022</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>motivations!$C$7:$C$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>26.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>26.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>25.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-35CA-4A2A-8D5F-BE1A6CBCD598}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="531029615"/>
+        <c:axId val="531027119"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="531029615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="531027119"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="531027119"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="531029615"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.27866797900262469"/>
+                  <c:y val="-0.48056333119807854"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>motivations!$J$7:$J$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2022</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>motivations!$K$7:$K$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8ECD-4D7E-9A76-0223983CF50A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="531029615"/>
+        <c:axId val="531027119"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="531029615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="531027119"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="531027119"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="2"/>
+          <c:min val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="531029615"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>157163</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>71438</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -709,6 +2785,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1519,7 +3684,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="3">
-        <f t="shared" ref="J47:J60" si="0">2/3</f>
+        <f t="shared" ref="J47:J58" si="0">2/3</f>
         <v>0.66666666666666663</v>
       </c>
     </row>
@@ -3580,4 +5745,966 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <f>F2*1.01^5</f>
+        <v>1.0510100500999999</v>
+      </c>
+      <c r="H2" s="3">
+        <f>G2*1.0081^5</f>
+        <v>1.0942711329791557</v>
+      </c>
+      <c r="I2" s="3">
+        <f>H2*1.0061^5</f>
+        <v>1.1280560721959558</v>
+      </c>
+      <c r="J2" s="3">
+        <f>I2*1.004^5</f>
+        <v>1.1507984060123795</v>
+      </c>
+      <c r="K2" s="3">
+        <f>J2*1.002^5</f>
+        <v>1.1623525141647169</v>
+      </c>
+      <c r="L2" s="3">
+        <f>K2*1.001^5</f>
+        <v>1.1681759118900195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <f>D2*(1-0.06)</f>
+        <v>0.94</v>
+      </c>
+      <c r="H2" s="3">
+        <f>F2*(1-0.06)</f>
+        <v>0.88359999999999994</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3">
+        <f>H2*(1-0.06)</f>
+        <v>0.83058399999999988</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <f>D3*(1-0.06)</f>
+        <v>0.94</v>
+      </c>
+      <c r="H3" s="3">
+        <f>F3*(1-0.06)</f>
+        <v>0.88359999999999994</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3">
+        <f>H3*(1-0.06)</f>
+        <v>0.83058399999999988</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M7">
+        <f>1-0.83</f>
+        <v>0.17000000000000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="13">
+        <f>(241822577+237201100)/(241822577+237201100+5856000+8368914)*100</f>
+        <v>97.116076100458642</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="13">
+        <f>100-E2</f>
+        <v>2.8839238995413581</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:V18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B2" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+    </row>
+    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="16"/>
+      <c r="J4" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="16"/>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="19"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="19"/>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B6" s="17"/>
+      <c r="C6" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="19"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="19"/>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B7" s="17">
+        <v>2012</v>
+      </c>
+      <c r="C7" s="18">
+        <v>26.2</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="19"/>
+      <c r="J7" s="17">
+        <v>2012</v>
+      </c>
+      <c r="K7" s="18">
+        <v>1.7</v>
+      </c>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="19"/>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B8" s="17">
+        <v>2013</v>
+      </c>
+      <c r="C8" s="18">
+        <v>26.1</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="19"/>
+      <c r="J8" s="17">
+        <v>2013</v>
+      </c>
+      <c r="K8" s="18">
+        <v>1.6</v>
+      </c>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="19"/>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B9" s="17">
+        <v>2014</v>
+      </c>
+      <c r="C9" s="18">
+        <v>26.7</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="19"/>
+      <c r="J9" s="17">
+        <v>2014</v>
+      </c>
+      <c r="K9" s="18">
+        <v>1.6</v>
+      </c>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="19"/>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B10" s="17">
+        <v>2015</v>
+      </c>
+      <c r="C10" s="18">
+        <v>26.6</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="19"/>
+      <c r="J10" s="17">
+        <v>2015</v>
+      </c>
+      <c r="K10" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="19"/>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B11" s="17">
+        <v>2016</v>
+      </c>
+      <c r="C11" s="18">
+        <v>27</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="19"/>
+      <c r="J11" s="17">
+        <v>2016</v>
+      </c>
+      <c r="K11" s="18">
+        <v>1.7</v>
+      </c>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="19"/>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B12" s="17">
+        <v>2017</v>
+      </c>
+      <c r="C12" s="18">
+        <v>25.7</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="19"/>
+      <c r="J12" s="17">
+        <v>2017</v>
+      </c>
+      <c r="K12" s="18">
+        <v>1.6</v>
+      </c>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="19"/>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B13" s="17">
+        <v>2018</v>
+      </c>
+      <c r="C13" s="18">
+        <v>25.4</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="19"/>
+      <c r="J13" s="17">
+        <v>2018</v>
+      </c>
+      <c r="K13" s="18">
+        <v>1.8</v>
+      </c>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="19"/>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B14" s="17">
+        <v>2019</v>
+      </c>
+      <c r="C14" s="18">
+        <v>25.8</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="19"/>
+      <c r="J14" s="17">
+        <v>2019</v>
+      </c>
+      <c r="K14" s="18">
+        <v>1.7</v>
+      </c>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="19"/>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B15" s="17">
+        <v>2020</v>
+      </c>
+      <c r="C15" s="18">
+        <v>25.3</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
+      <c r="J15" s="17">
+        <v>2020</v>
+      </c>
+      <c r="K15" s="18">
+        <v>1.7</v>
+      </c>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="19"/>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B16" s="17">
+        <v>2021</v>
+      </c>
+      <c r="C16" s="18">
+        <v>24.8</v>
+      </c>
+      <c r="D16" s="20"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="19"/>
+      <c r="J16" s="17">
+        <v>2021</v>
+      </c>
+      <c r="K16" s="18">
+        <v>1.7</v>
+      </c>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="19"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="17">
+        <v>2022</v>
+      </c>
+      <c r="C17" s="18">
+        <v>24.6</v>
+      </c>
+      <c r="D17" s="20"/>
+      <c r="E17" s="24">
+        <f>(C17-C7)/C7</f>
+        <v>-6.1068702290076257E-2</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="26"/>
+      <c r="H17" s="19"/>
+      <c r="J17" s="17">
+        <v>2022</v>
+      </c>
+      <c r="K17" s="18">
+        <v>1.7</v>
+      </c>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="19"/>
+    </row>
+    <row r="18" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="23"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/data/scenarios/food_as_industry.xlsx
+++ b/data/scenarios/food_as_industry.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11550" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="6615" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Regions" sheetId="7" r:id="rId1"/>
@@ -5989,7 +5989,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -5998,7 +5998,7 @@
     <col min="4" max="10" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>105</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>102</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>0.83058399999999988</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -6082,12 +6082,6 @@
       <c r="J3" s="3">
         <f>H3*(1-0.06)</f>
         <v>0.83058399999999988</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M7">
-        <f>1-0.83</f>
-        <v>0.17000000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/data/scenarios/food_as_industry.xlsx
+++ b/data/scenarios/food_as_industry.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="6615" firstSheet="1" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18360" windowHeight="6615" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Regions" sheetId="7" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="137">
   <si>
     <t>f_food</t>
   </si>
@@ -376,21 +376,9 @@
     <t>field machinery</t>
   </si>
   <si>
-    <t>diesel</t>
-  </si>
-  <si>
     <t>energy_source_share</t>
   </si>
   <si>
-    <t>biodiesel</t>
-  </si>
-  <si>
-    <t>hydrogen</t>
-  </si>
-  <si>
-    <t>electricity</t>
-  </si>
-  <si>
     <t>f_activity</t>
   </si>
   <si>
@@ -403,40 +391,52 @@
     <t>semi-natural grasslands</t>
   </si>
   <si>
+    <t>enteric_adj</t>
+  </si>
+  <si>
+    <t>f_species</t>
+  </si>
+  <si>
+    <t>bulls</t>
+  </si>
+  <si>
+    <t>beef</t>
+  </si>
+  <si>
+    <t>slaughter_share_male_as_steers</t>
+  </si>
+  <si>
+    <t>f_prod_system</t>
+  </si>
+  <si>
+    <t>slaughter_weight</t>
+  </si>
+  <si>
+    <t>f_crop</t>
+  </si>
+  <si>
+    <t>Semi-natural pastures</t>
+  </si>
+  <si>
+    <t>Semi-natural meadows</t>
+  </si>
+  <si>
+    <t>Diesel</t>
+  </si>
+  <si>
+    <t>Biodiesel</t>
+  </si>
+  <si>
+    <t>Hydrogen</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>cattle</t>
+  </si>
+  <si>
     <t>cows</t>
-  </si>
-  <si>
-    <t>enteric_adj</t>
-  </si>
-  <si>
-    <t>f_species</t>
-  </si>
-  <si>
-    <t>cattle</t>
-  </si>
-  <si>
-    <t>bulls</t>
-  </si>
-  <si>
-    <t>beef</t>
-  </si>
-  <si>
-    <t>slaughter_share_male_as_steers</t>
-  </si>
-  <si>
-    <t>f_prod_system</t>
-  </si>
-  <si>
-    <t>slaughter_weight</t>
-  </si>
-  <si>
-    <t>f_crop</t>
-  </si>
-  <si>
-    <t>Semi-natural pastures</t>
-  </si>
-  <si>
-    <t>Semi-natural meadows</t>
   </si>
 </sst>
 </file>
@@ -641,7 +641,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -673,6 +673,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2835,7 +2837,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s">
         <v>113</v>
@@ -2852,7 +2854,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
         <v>113</v>
@@ -5757,7 +5759,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5788,7 +5790,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B3" t="s">
         <v>111</v>
@@ -5802,7 +5804,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
         <v>111</v>
@@ -5837,7 +5839,7 @@
         <v>98</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>105</v>
@@ -5913,7 +5915,7 @@
         <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -5927,10 +5929,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -5947,10 +5949,10 @@
         <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -5964,13 +5966,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -6104,7 +6106,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>98</v>
@@ -6127,72 +6129,50 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
         <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="F2" s="31">
+        <v>1</v>
+      </c>
+      <c r="G2" s="31">
         <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="31">
+        <v>1</v>
+      </c>
+      <c r="G3" s="31">
         <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>0.5</v>
-      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6214,10 +6194,10 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -6238,19 +6218,19 @@
         <v>115</v>
       </c>
       <c r="B2" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="29" t="s">
-        <v>117</v>
-      </c>
       <c r="D2" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="32">
         <f>(241822577+237201100)/(241822577+237201100+5856000+8368914)*100</f>
         <v>97.116076100458642</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="31">
         <v>0</v>
       </c>
     </row>
@@ -6259,19 +6239,19 @@
         <v>115</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="32">
         <f>100-E2</f>
         <v>2.8839238995413581</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="31">
         <v>0</v>
       </c>
     </row>
@@ -6280,18 +6260,18 @@
         <v>115</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="32">
         <v>0</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="31">
         <v>0</v>
       </c>
     </row>
@@ -6300,18 +6280,18 @@
         <v>115</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="32">
         <v>0</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="31">
         <v>100</v>
       </c>
     </row>

--- a/data/scenarios/food_as_industry.xlsx
+++ b/data/scenarios/food_as_industry.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="243">
   <si>
     <t>f_food</t>
   </si>
@@ -767,6 +767,28 @@
   </si>
   <si>
     <t>assumes that biofuel production from straw increases to the current production of ethanol from wheat</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">JK: changed from 20kt org + 0kt conv --&gt; 10kt org + 10kt conv </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | HKP: doubling because the conventional export is still there??</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1139,7 +1161,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="sv-SE"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1281,7 +1303,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="531027119"/>
@@ -1323,7 +1345,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="531029615"/>
@@ -1365,7 +1387,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1464,7 +1486,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="sv-SE"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1606,7 +1628,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="531027119"/>
@@ -1650,7 +1672,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="sv-SE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="531029615"/>
@@ -1692,7 +1714,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="sv-SE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -8605,10 +8627,10 @@
         <v>206</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="E205" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F205" s="9"/>
       <c r="G205" s="9"/>
@@ -8616,7 +8638,7 @@
       <c r="I205" s="9"/>
       <c r="J205" s="9"/>
       <c r="K205" s="9">
-        <v>1</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
@@ -8641,10 +8663,10 @@
       <c r="I206" s="9"/>
       <c r="J206" s="9"/>
       <c r="K206" s="9">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="L206" s="9" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
